--- a/week-09/NorthwindTablesAndColumns.xlsx
+++ b/week-09/NorthwindTablesAndColumns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lesleyalberto\Documents\DataAnalytics\week-09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9340335E-623F-49A1-8509-41AC41C62D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAFFD80F-6191-467D-BBDF-E131B8059617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{901F5D27-877F-4C94-89AE-9A9B6ECE5CB6}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{901F5D27-877F-4C94-89AE-9A9B6ECE5CB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Northwind Columns" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="95">
   <si>
     <t>table_name</t>
   </si>
@@ -866,7 +866,7 @@
         <v>91</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -1018,7 +1018,7 @@
         <v>92</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>18</v>
@@ -1056,7 +1056,7 @@
         <v>92</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>19</v>
@@ -1094,7 +1094,7 @@
         <v>91</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>20</v>
@@ -1284,7 +1284,7 @@
         <v>91</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>25</v>
@@ -1626,7 +1626,7 @@
         <v>91</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>20</v>
@@ -1968,7 +1968,7 @@
         <v>92</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>40</v>
@@ -2538,7 +2538,7 @@
         <v>92</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>57</v>
@@ -2652,7 +2652,7 @@
         <v>91</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>60</v>
@@ -3374,7 +3374,7 @@
         <v>91</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>25</v>
@@ -3564,7 +3564,7 @@
         <v>91</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>20</v>
@@ -3754,7 +3754,7 @@
         <v>91</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>25</v>
@@ -3830,7 +3830,7 @@
         <v>91</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>79</v>
